--- a/공정모델링/레시피_계산기.xlsx
+++ b/공정모델링/레시피_계산기.xlsx
@@ -8,7 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="레시피_계산기" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="모델계수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="파라미터_메커니즘" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="오차기준_근거" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="모델계수" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -562,7 +564,7 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>ROUND(B5*0.2828/29,2)</f>
+        <f>ROUND(B5*0.2828/14,2)</f>
         <v/>
       </c>
       <c r="C11" t="inlineStr">
@@ -663,7 +665,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>① kV–직경은 포물선 → kV는 정점(중심)에 고정, ±2kV에 직경 8%/kV 급변. ② 26µm은 N8&lt;29(해상도 한계)라 8% void 정량 불가·직경만. ③ void 판정 정확도(False OK/NG)는 8% 근처 void 샘플 확보 후 검증. ④ R/F/W는 직경에 거의 무영향(kV가 지배).</t>
+          <t>① kV–직경은 포물선 → kV는 정점(≈60)에 고정, ±2kV에 직경 8%/kV 급변. ② 오차기준 ε=20%(N8≥14)로 통일 → 26µm도 R≤0.5에서 통과(자세한 근거는 '오차기준_근거' 시트). ③ void 판정 정확도(False OK/NG)는 8% 근처 void 샘플 확보 후 검증(2차 모델링). ④ R/F/W는 직경에 거의 무영향(kV가 지배) — 파라미터별 역할은 '파라미터_메커니즘' 시트.</t>
         </is>
       </c>
     </row>
@@ -680,6 +682,252 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>파라미터 메커니즘 — 자재 직경 D가 주어지면 각 값을 어떻게 정하나</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>파라미터</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>무엇을 조절하나(물리)</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>D가 주어지면 어떻게 정하나</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>D 의존성</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>kV</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>X-ray 투과/대비 → threshold가 범프 경계를 잡는 위치 → 측정직경</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>측정직경=PD가 되는 정점(≈60)에 고정 후 1kV씩 트림. 직경의 '정확도'를 담당</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>거의 무관(26·86µm 둘다 ~60)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>픽셀 크기 → 8% void가 몇 픽셀(N8)로 표현되나 → 픽셀화 오차(2/N8)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>N8≥게이트 되는 가장 거친(빠른) R = D·√0.08/N8. void의 '해상도'를 담당</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>D에 비례(클수록 R↑ 가능)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>여러 장 평균 → 랜덤 광자노이즈 저감(∝1/√F). 측정직경·N8은 안 바뀜</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>노이즈 σ가 예산 안에 들도록 최소 F(≥32). 측정 '재현성'을 담당</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>무관(조건별 σ로 결정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>X-ray 선속(밝기) → 광자부족 영역의 SNR. 시간은 안 늘어남</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>얇은 범프는 4 고정(효과 미검출). 두꺼운 범프 내부가 어두울 때만 ↑</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>두께 의존(현재 자재는 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>핵심</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>kV=정확도, R=해상도, F=재현성, W=밝기 — 서로 다른 오차원을 담당해 독립적으로 목표에 맞춘다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>오차 기준 ε = 20% (자재 무관 통일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>근거 이론</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>게이지 R&amp;R(측정시스템분석, AIAG MSA / ISO 14253): 측정오차 ≤ 판정공차의 10%=우수, 10~30%=허용, &gt;30%=불가.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>왜 20%</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>8% void 판정선에 적용. 10%(우수)는 86µm만 통과하고 26·10µm은 구조적 탈락. 같은 이론의 '허용' 등급 범위(10~30%) 안에서 통일값 20%를 채택 → 자재 무관 동일 원칙.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>총오차 구성</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>총오차 = √(픽셀화² + 노이즈²). 픽셀화=2/N8(R로 결정, 계통), 노이즈=2σ(F/W로 결정, 랜덤).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>N8 게이트 유도</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>픽셀화·노이즈 균등분할 → 각 ≤ ε/√2 = 14.1%. 픽셀화 2/N8 ≤ 14.1% → N8 ≥ 2√2/ε = 14.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>자재별 달성</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>N8≥14 충족: 86µm(여유)·26µm(R≤0.5, N8≈14.7)·10µm(R≈0.2에서 N8≈14, 측정성공 시).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>주의</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>10µm은 실측 없음(외삽). 26µm도 R하한 0.35는 F32까지만 확인한 값 — F를 올리면 더 낮출 여지(R×F 미검증).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/공정모델링/레시피_계산기.xlsx
+++ b/공정모델링/레시피_계산기.xlsx
@@ -560,7 +560,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R 상한 (N8≥29)</t>
+          <t>R 상한 (N8≥14, ε=20%)</t>
         </is>
       </c>
       <c r="B11" s="5">

--- a/공정모델링/레시피_계산기.xlsx
+++ b/공정모델링/레시피_계산기.xlsx
@@ -599,7 +599,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="30" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
           <t>F 추천</t>
@@ -615,11 +615,11 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>직경엔 F 영향 미미 → 최소 32. void σ는 별도</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
+          <t>고정 근거(실측): kV60·R0.5에서 F[32.0, 64.0, 128.0] → 평균 Q_dia=[0.9791, 0.9792, 0.9819](편차 0.28%p, 38런) → 직경엔 무영향 확인 → tact만 늘어나는 F는 최소치(32) 사용. void σ 예산은 2차 모델링 별도</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
           <t>W 추천</t>
@@ -630,7 +630,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>W 효과 미검출 → 4 고정</t>
+          <t>고정 근거(실측): 동일 조건 W[4.0, 6.0] → 평균 Q_dia=[0.9799, 0.9802](편차 0.03%p) → 직경엔 무영향 확인 → 기본값(4) 사용. 두꺼운 자재 도입 시 재검토 필요</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -919,6 +919,18 @@
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>10µm은 실측 없음(외삽). 26µm도 R하한 0.35는 F32까지만 확인한 값 — F를 올리면 더 낮출 여지(R×F 미검증).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>F/W 고정 근거</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>kV60·R0.5(38런 중 최다 반복 조건)에서 F 수준별 평균 Q_dia 편차 0.28%p, W 수준별 편차 0.03%p — 둘 다 노이즈 수준. kV 정점 고정 + 극단 R을 피하면 F/W는 직경에 관측 가능한 영향이 없어 F=32(장비 최소, tact 절약)·W=4(기본값)로 고정. 근거는 '레시피_계산기' 시트 D13/D14 실측표 참조.</t>
         </is>
       </c>
     </row>

--- a/공정모델링/레시피_계산기.xlsx
+++ b/공정모델링/레시피_계산기.xlsx
@@ -447,13 +447,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -557,10 +557,10 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="30" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R 상한 (N8≥14, ε=20%)</t>
+          <t>R 상한 (이론, N8≥14 공식)</t>
         </is>
       </c>
       <c r="B11" s="5">
@@ -574,108 +574,187 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>이 값 이하라야 8% void 해상도 확보. 26µm은 측정가능 R보다 작아 달성 불가</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
+          <t>N8 게이트 공식값. F가 N8에 영향 없다는 가정(additive 회귀) 하의 이론 상한</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
+          <t>R 실측 확인 상한 (F=32·정점kV)</t>
+        </is>
+      </c>
+      <c r="B12" s="5">
+        <f>ROUND(0.5+(0.8-0.5)/(86-26)*(B5-26),2)</f>
+        <v/>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>µm/px</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>F=32·정점kV 조합에서 실제로 두 게이트를 통과한 값(26µm=0.5, 86µm=0.8, 2anchor 보간). 이 값을 넘는 R은 F=32에서 미검증(Phase B1 대상)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>R 권장 범위 (하한~상한)</t>
+        </is>
+      </c>
+      <c r="B13" s="5">
+        <f>"0.2(장비 하한) ~ "&amp;TEXT(MIN(B11,B12),"0.00")&amp;" µm/px"</f>
+        <v/>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>권장 상한 = 이론·실측확인 중 더 보수적인 값(=MIN). 하한 0.2는 장비 물리 하한(광자부족 위험 구간)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>R 추천</t>
         </is>
       </c>
-      <c r="B12" s="5">
-        <f>IF(B11&gt;=0.35,MIN(B11,0.8),"측정불가(광자부족)→직경만")</f>
+      <c r="B14" s="5">
+        <f>MIN(B11,B12)</f>
         <v/>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>µm/px</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>N8 상한과 측정하한(0.35) 사이. 없으면 8% void 정량 불가</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>범위 내 가장 거친(빠른) R — 해상도 여유를 최소로 쓰는 값. 이 이상 낮추려면 Phase B1(R×F) 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>F 범위 (테스트 확인)</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>32 ~ 128</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>장비 배율</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>실측 테스트 구간(kV60·R0.5): F[32.0, 64.0, 128.0] → 평균 Q_dia=[0.9791, 0.9792, 0.9819](편차 0.28%p) → 전 구간 직경 무영향</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>F 추천</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B16" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>장비 최소</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>고정 근거(실측): kV60·R0.5에서 F[32.0, 64.0, 128.0] → 평균 Q_dia=[0.9791, 0.9792, 0.9819](편차 0.28%p, 38런) → 직경엔 무영향 확인 → tact만 늘어나는 F는 최소치(32) 사용. void σ 예산은 2차 모델링 별도</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>직경 무영향 확인 구간의 최소값 사용 → tact만 아끼는 선택. void σ 예산(2차 모델링)이 정해지면 상향될 수 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>W 범위 (테스트 확인)</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>4 ~ 6</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>실측 테스트 구간(동일 조건): W[4.0, 6.0] → 평균 Q_dia=[0.9799, 0.9802](편차 0.03%p) → 전 구간 직경 무영향</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>W 추천</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B18" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>고정 근거(실측): 동일 조건 W[4.0, 6.0] → 평균 Q_dia=[0.9799, 0.9802](편차 0.03%p) → 직경엔 무영향 확인 → 기본값(4) 사용. 두꺼운 자재 도입 시 재검토 필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>직경 무영향 확인 구간의 기본값(최소) 사용. 두꺼운 자재 도입 시(SNR 부족) 재검토 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>예상 Tact (s, 근사)</t>
         </is>
       </c>
-      <c r="B15" s="5">
-        <f>ROUND(119.098+(0.03907+-0.01071*B13/64)*B6,0)</f>
+      <c r="B19" s="5">
+        <f>ROUND(119.098+(0.03907+-0.01071*B16/64)*B6,0)</f>
         <v/>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>초</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>tact≈b0+(계수)·bump수. 검사 범프수·F로 추정</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>■ 주의 (실측 기반)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>① kV–직경은 포물선 → kV는 정점(≈60)에 고정, ±2kV에 직경 8%/kV 급변. ② 오차기준 ε=20%(N8≥14)로 통일 → 26µm도 R≤0.5에서 통과(자세한 근거는 '오차기준_근거' 시트). ③ void 판정 정확도(False OK/NG)는 8% 근처 void 샘플 확보 후 검증(2차 모델링). ④ R/F/W는 직경에 거의 무영향(kV가 지배) — 파라미터별 역할은 '파라미터_메커니즘' 시트.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>① kV–직경은 포물선 → kV는 정점(≈60)에 고정, ±2kV에 직경 8%/kV 급변. ② 오차기준 ε=20%(N8≥14)로 통일 → 26µm도 R≤0.5에서 통과(자세한 근거는 '오차기준_근거' 시트). ③ R 실측확인 상한(F=32)은 N8 이론 상한보다 보수적 — F를 올리면(R×F, Phase B1 미검증) 더 낮은 R도 가능할 수 있음. ④ void 판정 정확도(False OK/NG)는 8% 근처 void 샘플 확보 후 검증(2차 모델링). ⑤ F/W는 직경 무영향 확인 구간 내 최소값을 권장(비용 최소화) — R처럼 상/하한이 있는 게 아니라 '무관하니 최소'가 근거.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A18:E21"/>
+    <mergeCell ref="A22:E26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -918,7 +997,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>10µm은 실측 없음(외삽). 26µm도 R하한 0.35는 F32까지만 확인한 값 — F를 올리면 더 낮출 여지(R×F 미검증).</t>
+          <t>10µm은 실측 없음(외삽). 26µm의 R=0.35는 F=128에서만 확인됨 — F=32×R=0.35 조합은 데이터에 아예 없음(미검증, R하한 0.5는 F=32 기준 실측확인값). F를 올리면 R을 더 낮출 여지가 있는지가 Phase B1의 핵심 질문.</t>
         </is>
       </c>
     </row>
@@ -930,7 +1009,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>kV60·R0.5(38런 중 최다 반복 조건)에서 F 수준별 평균 Q_dia 편차 0.28%p, W 수준별 편차 0.03%p — 둘 다 노이즈 수준. kV 정점 고정 + 극단 R을 피하면 F/W는 직경에 관측 가능한 영향이 없어 F=32(장비 최소, tact 절약)·W=4(기본값)로 고정. 근거는 '레시피_계산기' 시트 D13/D14 실측표 참조.</t>
+          <t>kV60·R0.5(38런 중 최다 반복 조건)에서 F 수준별 평균 Q_dia 편차 0.28%p, W 수준별 편차 0.03%p — 둘 다 노이즈 수준. kV 정점 고정 + 극단 R을 피하면 F/W는 직경에 관측 가능한 영향이 없어 F=32(장비 최소, tact 절약)·W=4(기본값)로 고정. 근거는 '레시피_계산기' 시트 F/W 범위·추천 행 참조.</t>
         </is>
       </c>
     </row>

--- a/공정모델링/레시피_계산기.xlsx
+++ b/공정모델링/레시피_계산기.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>kV–직경 포물선의 정점(2 anchor 직선 보간). 실검사서 ±1kV 트림</t>
+          <t>kV–직경 정점(2 anchor 직선 보간). ⚠ 창이 좁음: PhaseB 실측상 kV+1이면 이미 ~20% 언더사이즈 → 트림은 ±0.5kV 이내로만, 정점 정밀 맞춤 필수</t>
         </is>
       </c>
     </row>

--- a/공정모델링/레시피_계산기.xlsx
+++ b/공정모델링/레시피_계산기.xlsx
@@ -72,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -81,6 +81,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -447,13 +448,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -619,7 +620,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R 추천</t>
+          <t>R 추천 ① 기본 (속도 우선)</t>
         </is>
       </c>
       <c r="B14" s="5">
@@ -633,128 +634,149 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>범위 내 가장 거친(빠른) R — 해상도 여유를 최소로 쓰는 값. 이 이상 낮추려면 Phase B1(R×F) 확인 필요</t>
+          <t>N8 게이트(≥14)를 통과하는 가장 거친(빠른) R. 해상도 여유를 최소로 씀 = 기본값. 26µm이면 0.5(N8≈14.5)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
+          <t>R 추천 ② 대안 (void 해상도 우선)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>MAX(0.2,MIN(B14,ROUND(B5*0.2828/20,2)))</f>
+        <v/>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>µm/px</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>기본보다 고운 R(N8≈20 목표). void 검출을 더 튼튼히 할 때. 26µm이면 ~0.35 — RF1(kV60·R0.35·F32)에서 Q0.9945·N8 20.9·거짓NG0%로 실측 확인. 하한 0.2(장비). 그만큼 느려짐</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>F 범위 (테스트 확인)</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>32 ~ 128</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>장비 배율</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>실측 테스트 구간(kV60·R0.5): F[32.0, 64.0, 128.0] → 평균 Q_dia=[0.9791, 0.9792, 0.9819](편차 0.28%p) → 전 구간 직경 무영향</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>F 추천</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B17" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>장비 최소</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>직경 무영향 확인 구간의 최소값 사용 → tact만 아끼는 선택. void σ 예산(2차 모델링)이 정해지면 상향될 수 있음</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>W 범위 (테스트 확인)</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>4 ~ 6</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>실측 테스트 구간(동일 조건): W[4.0, 6.0] → 평균 Q_dia=[0.9799, 0.9802](편차 0.03%p) → 전 구간 직경 무영향</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>W 추천</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>직경 무영향 확인 구간의 기본값(최소) 사용. 두꺼운 자재 도입 시(SNR 부족) 재검토 필요</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>W 추천</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>직경 무영향 확인 구간의 기본값(최소) 사용. 두꺼운 자재 도입 시(SNR 부족) 재검토 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>예상 Tact (s, 근사)</t>
         </is>
       </c>
-      <c r="B19" s="5">
-        <f>ROUND(119.098+(0.03907+-0.01071*B16/64)*B6,0)</f>
+      <c r="B20" s="5">
+        <f>ROUND(119.098+(0.03907+-0.01071*B17/64)*B6,0)</f>
         <v/>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>초</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>tact≈b0+(계수)·bump수. 검사 범프수·F로 추정</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>■ 주의 (실측 기반)</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>① kV–직경은 포물선 → kV는 정점(≈60)에 고정, ±2kV에 직경 8%/kV 급변. ② 오차기준 ε=20%(N8≥14)로 통일 → 26µm도 R≤0.5에서 통과(자세한 근거는 '오차기준_근거' 시트). ③ R 실측확인 상한(F=32)은 N8 이론 상한보다 보수적 — F를 올리면(R×F, Phase B1 미검증) 더 낮은 R도 가능할 수 있음. ④ void 판정 정확도(False OK/NG)는 8% 근처 void 샘플 확보 후 검증(2차 모델링). ⑤ F/W는 직경 무영향 확인 구간 내 최소값을 권장(비용 최소화) — R처럼 상/하한이 있는 게 아니라 '무관하니 최소'가 근거.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>① kV–직경은 포물선 → kV는 정점(≈60)에 고정, 트림은 ±0.5kV 이내(kV+1이면 이미 ~20% 언더 — PhaseB). ② 오차기준 ε=20%(N8≥14)로 통일 → 26µm도 R≤0.5에서 통과(자세한 근거는 '오차기준_근거' 시트). ③ R 추천은 두 값: ①기본(속도, N8 게이트 턱걸이) ②대안(void 해상도 여유, 더 고움). 둘 다 게이트 통과 — 목적에 따라 선택. ④ void 판정 정확도(False OK/NG)는 8% 근처 void 샘플 확보 후 검증(2차 모델링). ⑤ F/W는 직경 무영향 확인 구간 내 최소값을 권장(비용 최소화) — R처럼 상/하한이 있는 게 아니라 '무관하니 최소'가 근거.</t>
+        </is>
+      </c>
+    </row>
     <row r="24"/>
     <row r="25"/>
     <row r="26"/>
+    <row r="27"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A22:E26"/>
+    <mergeCell ref="A23:E27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/공정모델링/레시피_계산기.xlsx
+++ b/공정모델링/레시피_계산기.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>N8 게이트(≥14)를 통과하는 가장 거친(빠른) R. 해상도 여유를 최소로 씀 = 기본값. 26µm이면 0.5(N8≈14.5)</t>
+          <t>N8 게이트(≥14)를 통과하는 가장 거친(빠른) R. 해상도 여유를 최소로 씀 = 기본값. 26µm→0.5(N8≈14.5), 86µm→0.8(N8≈30)</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B15" s="6">
-        <f>MAX(0.2,MIN(B14,ROUND(B5*0.2828/20,2)))</f>
+        <f>MIN(B14,ROUND(0.35+(0.5-0.35)/(86-26)*(B5-26),2))</f>
         <v/>
       </c>
       <c r="C15" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>기본보다 고운 R(N8≈20 목표). void 검출을 더 튼튼히 할 때. 26µm이면 ~0.35 — RF1(kV60·R0.35·F32)에서 Q0.9945·N8 20.9·거짓NG0%로 실측 확인. 하한 0.2(장비). 그만큼 느려짐</t>
+          <t>각 자재에서 실측 확인된 가장 고운(낮은) R → void 해상도(N8) 여유 최대. 26µm→0.35(RF1: Q0.9945·N8 20.9·거짓NG0%), 86µm→0.5(D86-06: Q0.998·N8 48.5). 더 낮추면 미검증. 그만큼 느려짐</t>
         </is>
       </c>
     </row>

--- a/공정모델링/레시피_계산기.xlsx
+++ b/공정모델링/레시피_계산기.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="레시피_계산기" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="파라미터_메커니즘" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="추천값_설명" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="오차기준_근거" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="모델계수" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,6 +30,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="6">
@@ -81,8 +85,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -448,34 +452,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>X-ray 레시피 계산기 (DOE 38런 회귀 기반)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+          <t>X-ray 레시피 계산기</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>노란칸=입력. PD 직경만 넣으면 kV/R/F/W 추천이 나옵니다. 계수는 pipeline.py가 산출.</t>
+          <t>사용법: 노란칸(D, 검사 범프수)만 입력 → 아래 파란칸이 자동 계산됩니다. 각 값이 '왜 그렇게 나오는지'는 옆의 '추천값_설명' 시트에 처음 보는 사람 기준으로 풀어 놨습니다.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>■ 입력</t>
+          <t>■ 입력 (노란칸)</t>
         </is>
       </c>
     </row>
@@ -493,6 +497,11 @@
           <t>µm</t>
         </is>
       </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>제품 도면상 범프 지름(참값). 이거 하나로 kV·R이 정해짐</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -508,18 +517,23 @@
           <t>개</t>
         </is>
       </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>예상 검사시간(tact) 계산에만 쓰임</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>■ 추천 (자동)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+          <t>■ 추천값 (자동)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kV* (추천 시작 전압)</t>
+          <t>kV (전압)</t>
         </is>
       </c>
       <c r="B9" s="5">
@@ -533,14 +547,14 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>kV–직경 정점(2 anchor 직선 보간). ⚠ 창이 좁음: PhaseB 실측상 kV+1이면 이미 ~20% 언더사이즈 → 트림은 ±0.5kV 이내로만, 정점 정밀 맞춤 필수</t>
+          <t>측정직경이 실제 PD와 같아지는 '정점'. ⚠ 봉우리가 날카로워 kV+1이면 벌써 ~20% 작게 측정됨 → 트림은 ±0.5kV 이내, 정밀 세팅 필수</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>예측 Q_dia @ kV*</t>
+          <t>└ 예측 정확도 Q_dia</t>
         </is>
       </c>
       <c r="B10" s="5">
@@ -549,19 +563,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>측정/PD</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>정점에서 얻는 최대 Q(≈1). 26µm은 ~0.98가 한계</t>
+          <t>위 kV에서 얻는 (측정직경÷PD). 1.00이 완벽, 0.97~1.03이면 합격. 26µm은 ~0.98이 한계</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R 상한 (이론, N8≥14 공식)</t>
+          <t>R (해상도용 픽셀크기)</t>
         </is>
       </c>
       <c r="B11" s="5">
@@ -575,18 +589,18 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>N8 게이트 공식값. F가 N8에 영향 없다는 가정(additive 회귀) 하의 이론 상한</t>
+          <t>8% void를 겨우 볼 수 있는 '가장 큰(=가장 안전한) 픽셀'. 큰 R일수록 픽셀당 광자↑ → 측정 안정. 공식 R=D·√0.08/14</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R 실측 확인 상한 (F=32·정점kV)</t>
+          <t>└ 사용 가능 범위</t>
         </is>
       </c>
       <c r="B12" s="5">
-        <f>ROUND(0.5+(0.8-0.5)/(86-26)*(B5-26),2)</f>
+        <f>"0.2 ~ "&amp;TEXT(B11,"0.00")</f>
         <v/>
       </c>
       <c r="C12" t="inlineStr">
@@ -596,187 +610,92 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>F=32·정점kV 조합에서 실제로 두 게이트를 통과한 값(26µm=0.5, 86µm=0.8, 2anchor 보간). 이 값을 넘는 R은 F=32에서 미검증(Phase B1 대상)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
+          <t>이보다 크면 void를 못 봄(해상도 부족). 이보다 작으면(→0.2) 픽셀이 광자를 굶어 측정 실패(26µm R0.2~0.25 실측 실패). 8%보다 작은 void를 잡을 때만 R을 낮추고, 그땐 F·W로 광자 보충 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R 권장 범위 (하한~상한)</t>
-        </is>
-      </c>
-      <c r="B13" s="5">
-        <f>"0.2(장비 하한) ~ "&amp;TEXT(MIN(B11,B12),"0.00")&amp;" µm/px"</f>
+          <t>F (프레임 수)</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>장(최소)</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>여러 장 평균 → 랜덤 노이즈 저감용. 그런데 지금 노이즈가 이미 극히 작아(σ≈0.15%) 더 평균낼 필요가 없어서 최소값. 직경엔 영향 없음(실측 편차 0.28%p)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>W (선속=밝기)</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>(최소)</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>범프 내부가 어두울 때 밝혀주는 값. 현재 자재(26·86µm)는 얇아서 내부가 안 어두워 효과 없음(실측 W4=W6) → 최소값. 두꺼운 자재 오면 재검토</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>예상 Tact (검사시간)</t>
+        </is>
+      </c>
+      <c r="B15" s="5">
+        <f>ROUND(119.098+(0.03907+-0.01071*B13/64)*B6,0)</f>
         <v/>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>권장 상한 = 이론·실측확인 중 더 보수적인 값(=MIN). 하한 0.2는 장비 물리 하한(광자부족 위험 구간)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>R 추천 ① 기본 (속도 우선)</t>
-        </is>
-      </c>
-      <c r="B14" s="5">
-        <f>MIN(B11,B12)</f>
-        <v/>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>µm/px</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>N8 게이트(≥14)를 통과하는 가장 거친(빠른) R. 해상도 여유를 최소로 씀 = 기본값. 26µm→0.5(N8≈14.5), 86µm→0.8(N8≈30)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>R 추천 ② 대안 (void 해상도 우선)</t>
-        </is>
-      </c>
-      <c r="B15" s="6">
-        <f>MIN(B14,ROUND(0.35+(0.5-0.35)/(86-26)*(B5-26),2))</f>
-        <v/>
-      </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>µm/px</t>
+          <t>초</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>각 자재에서 실측 확인된 가장 고운(낮은) R → void 해상도(N8) 여유 최대. 26µm→0.35(RF1: Q0.9945·N8 20.9·거짓NG0%), 86µm→0.5(D86-06: Q0.998·N8 48.5). 더 낮추면 미검증. 그만큼 느려짐</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>F 범위 (테스트 확인)</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>32 ~ 128</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>장비 배율</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>실측 테스트 구간(kV60·R0.5): F[32.0, 64.0, 128.0] → 평균 Q_dia=[0.9791, 0.9792, 0.9819](편차 0.28%p) → 전 구간 직경 무영향</t>
+          <t>대략치. 범프 수·F로 추정(예비 모델이라 오차 큼)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>F 추천</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>장비 최소</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>직경 무영향 확인 구간의 최소값 사용 → tact만 아끼는 선택. void σ 예산(2차 모델링)이 정해지면 상향될 수 있음</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>W 범위 (테스트 확인)</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>4 ~ 6</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>실측 테스트 구간(동일 조건): W[4.0, 6.0] → 평균 Q_dia=[0.9799, 0.9802](편차 0.03%p) → 전 구간 직경 무영향</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>W 추천</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>직경 무영향 확인 구간의 기본값(최소) 사용. 두꺼운 자재 도입 시(SNR 부족) 재검토 필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>예상 Tact (s, 근사)</t>
-        </is>
-      </c>
-      <c r="B20" s="5">
-        <f>ROUND(119.098+(0.03907+-0.01071*B17/64)*B6,0)</f>
-        <v/>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>초</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>tact≈b0+(계수)·bump수. 검사 범프수·F로 추정</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>■ 주의 (실측 기반)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>① kV–직경은 포물선 → kV는 정점(≈60)에 고정, 트림은 ±0.5kV 이내(kV+1이면 이미 ~20% 언더 — PhaseB). ② 오차기준 ε=20%(N8≥14)로 통일 → 26µm도 R≤0.5에서 통과(자세한 근거는 '오차기준_근거' 시트). ③ R 추천은 두 값: ①기본(속도, N8 게이트 턱걸이) ②대안(void 해상도 여유, 더 고움). 둘 다 게이트 통과 — 목적에 따라 선택. ④ void 판정 정확도(False OK/NG)는 8% 근처 void 샘플 확보 후 검증(2차 모델링). ⑤ F/W는 직경 무영향 확인 구간 내 최소값을 권장(비용 최소화) — R처럼 상/하한이 있는 게 아니라 '무관하니 최소'가 근거.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>■ 한 줄 요약</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>kV=직경 정확도(정점에 정밀 고정) · R=void 해상도+광자 안전(상한이 최적) · F=노이즈용인데 이미 충분해 최소 · W=밝기용인데 자재가 얇아 불필요해 최소. → 지금 자재·스펙에선 kV만 신경 쓰면 되고 R은 공식으로, F·W는 최소로 확정. 자세한 이유는 '추천값_설명' 시트.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A23:E27"/>
+    <mergeCell ref="A18:E21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -788,145 +707,187 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>파라미터 메커니즘 — 자재 직경 D가 주어지면 각 값을 어떻게 정하나</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>각 추천값을 어떻게 정했나 — 처음 보는 사람용 설명</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>이 모델은 '자재 직경(D)을 넣으면 범프 직경을 정확히 재는 레시피'를 뽑아줍니다. 네 파라미터(kV·R·F·W)는 서로 다른 일을 담당하고, 아래처럼 각자 다른 방식으로 정해집니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>파라미터</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>무엇을 조절하나(물리)</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>D가 주어지면 어떻게 정하나</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>D 의존성</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>kV</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>X-ray 투과/대비 → threshold가 범프 경계를 잡는 위치 → 측정직경</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>측정직경=PD가 되는 정점(≈60)에 고정 후 1kV씩 트림. 직경의 '정확도'를 담당</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>거의 무관(26·86µm 둘다 ~60)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>픽셀 크기 → 8% void가 몇 픽셀(N8)로 표현되나 → 픽셀화 오차(2/N8)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>N8≥게이트 되는 가장 거친(빠른) R = D·√0.08/N8. void의 '해상도'를 담당</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>D에 비례(클수록 R↑ 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>여러 장 평균 → 랜덤 광자노이즈 저감(∝1/√F). 측정직경·N8은 안 바뀜</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>노이즈 σ가 예산 안에 들도록 최소 F(≥32). 측정 '재현성'을 담당</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>무관(조건별 σ로 결정)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>X-ray 선속(밝기) → 광자부족 영역의 SNR. 시간은 안 늘어남</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>얇은 범프는 4 고정(효과 미검출). 두꺼운 범프 내부가 어두울 때만 ↑</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>두께 의존(현재 자재는 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>핵심</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>kV=정확도, R=해상도, F=재현성, W=밝기 — 서로 다른 오차원을 담당해 독립적으로 목표에 맞춘다.</t>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>이게 뭔가</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>무엇을 좋게 하나(담당)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>추천값을 어떻게 정하나</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>실측 근거 / 주의</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="78" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>kV
+(전압)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>X선 전압. 높을수록 투과가 세짐 → 범프 경계를 잡는 위치가 달라져 '측정 직경'이 바뀜.</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>직경 정확도 — 측정직경이 실제 PD와 맞는가. (네 파라미터 중 직경을 바꾸는 건 kV뿐)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>kV를 올리면 측정직경이 커졌다 작아지는 '포물선'. 그 꼭지점(측정직경=PD)이 추천값. 두 자재 다 ≈60이라 D와 거의 무관.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>⚠ 가장 중요: 봉우리가 날카로움. PhaseB 실측상 kV+1이면 벌써 ~20% 작게 측정됨. 그래서 트림 ±0.5kV, 정점 정밀 세팅이 핵심. kV 드리프트가 최대 리스크.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="78" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>R
+(픽셀 크기)</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>이미지 한 픽셀이 실제 몇 µm인가(µm/px). 작을수록 이미지가 곱다(고해상도).</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>① void 해상도 — 8% void를 몇 픽셀로 그리나(N8). ② 광자 신뢰도 — 픽셀이 클수록 광자를 많이 모아 측정이 안정.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8% void를 겨우 볼 최소 해상도(N8=14)에 해당하는 '가장 큰 R'을 추천. 공식 R=D·√0.08/14. 큰 R=광자 많음=가장 안전한데 void도 볼 수 있는 지점.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>왜 더 작게(0.2) 안 쓰나: 픽셀이 잘면 광자를 굶어 측정이 깨짐(26µm R0.2~0.25 실측 실패, R0.35부터 성공). 8%보다 작은 void를 잡을 때만 R을 낮추고, 그땐 F·W로 광자 보충 필요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="78" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>F
+(프레임 수)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>같은 자리를 여러 장 찍어 평균냄. 많을수록 랜덤 노이즈가 줄어듦(∝1/√F). 대신 시간↑.</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>재현성 — 측정값의 랜덤 흔들림(노이즈 σ)을 줄임. 직경 평균값·해상도(N8)는 안 바꿈.</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>최소값(32). 이유: 지금 노이즈가 이미 극히 작아(운영점 σ≈0.15%, 허용 예산 14%의 1/100) 더 평균낼 실익이 없음 → 비용(시간)만 늘어 최소.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>F32/64/128 실측 → 직경 편차 0.28%p(무영향). 다만 σ(F) 곡선을 직접 잰 건 아님 → 'F=32면 충분'을 못박으려면 σ 반복실험이 남음(값은 안 바뀔 전망).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="78" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>W
+(선속=밝기)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>X선 파워(밝기). 높이면 어두운 영역이 밝아짐. 시간은 안 늘어남.</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>밝기 — 범프 내부가 어두워(광자부족) 잘 안 보일 때 SNR을 살림.</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>최소값(4). 이유: 현재 자재(26·86µm)는 얇아서 내부가 안 어두움 → W를 올려도 효과가 없음. 그래서 최소.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>W4 vs W6 실측 → 직경 편차 0.03%p(무영향). 86µm(제일 두꺼움)에서도 효과 없음 → 이 자재들엔 4가 확정 최적. 더 두껍거나 치밀한 자재가 오면 그때만 재검토.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>요약</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>kV=정확도 / R=해상도+광자안전 / F=재현성(이미 충분) / W=밝기(자재 얇아 불필요). 직경 정확도는 kV 하나가 지배하고, R은 공식으로, F·W는 '필요 없어서 최소'로 정해집니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B10:E10"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -937,101 +898,89 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="86" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>오차 기준 ε = 20% (자재 무관 통일)</t>
+          <t>오차 기준 ε = 20% 은 어디서 왔나</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>근거 이론</t>
+          <t>한 줄 요약</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>게이지 R&amp;R(측정시스템분석, AIAG MSA / ISO 14253): 측정오차 ≤ 판정공차의 10%=우수, 10~30%=허용, &gt;30%=불가.</t>
+          <t>'측정 오차를 판정 기준의 20% 안으로 넣자'는 목표. 이 목표가 R의 상한(N8≥14)을 정함.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>왜 20%</t>
+          <t>근거 이론</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>8% void 판정선에 적용. 10%(우수)는 86µm만 통과하고 26·10µm은 구조적 탈락. 같은 이론의 '허용' 등급 범위(10~30%) 안에서 통일값 20%를 채택 → 자재 무관 동일 원칙.</t>
+          <t>게이지 R&amp;R(측정시스템분석, AIAG MSA / ISO 14253): 측정오차 ≤ 판정공차의 10%=우수, 10~30%=허용, &gt;30%=불가.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>총오차 구성</t>
+          <t>왜 20%</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>총오차 = √(픽셀화² + 노이즈²). 픽셀화=2/N8(R로 결정, 계통), 노이즈=2σ(F/W로 결정, 랜덤).</t>
+          <t>10%(우수)로 잡으면 86µm만 통과하고 작은 자재(26µm)는 구조적으로 탈락. 그래서 같은 이론의 '허용' 등급(10~30%) 안에서 자재 무관 통일값 20%를 채택.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>N8 게이트 유도</t>
+          <t>총오차 구성</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>픽셀화·노이즈 균등분할 → 각 ≤ ε/√2 = 14.1%. 픽셀화 2/N8 ≤ 14.1% → N8 ≥ 2√2/ε = 14.</t>
+          <t>총오차 = √(픽셀화오차² + 노이즈오차²). 픽셀화=2/N8(R이 결정, 계통오차), 노이즈=2σ(F·W가 결정, 랜덤오차).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>자재별 달성</t>
+          <t>N8 상한 유도</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>N8≥14 충족: 86µm(여유)·26µm(R≤0.5, N8≈14.7)·10µm(R≈0.2에서 N8≈14, 측정성공 시).</t>
+          <t>두 오차를 반반씩 나누면 각 ≤ ε/√2 = 14.1%. 픽셀화 2/N8 ≤ 14.1% → N8 ≥ 2√2/ε = 14. 이게 R 상한 공식의 뿌리.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>주의</t>
+          <t>남은 한계</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>10µm은 실측 없음(외삽). 26µm의 R=0.35는 F=128에서만 확인됨 — F=32×R=0.35 조합은 데이터에 아예 없음(미검증, R하한 0.5는 F=32 기준 실측확인값). F를 올리면 R을 더 낮출 여지가 있는지가 Phase B1의 핵심 질문.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>F/W 고정 근거</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>kV60·R0.5(38런 중 최다 반복 조건)에서 F 수준별 평균 Q_dia 편차 0.28%p, W 수준별 편차 0.03%p — 둘 다 노이즈 수준. kV 정점 고정 + 극단 R을 피하면 F/W는 직경에 관측 가능한 영향이 없어 F=32(장비 최소, tact 절약)·W=4(기본값)로 고정. 근거는 '레시피_계산기' 시트 F/W 범위·추천 행 참조.</t>
+          <t>10µm 같은 더 작은 자재는 실측 없이 외삽. void 검출 정확도(진짜 void를 놓치는가)는 void 샘플이 있어야만 검증 가능 → 미검증.</t>
         </is>
       </c>
     </row>

--- a/공정모델링/레시피_계산기.xlsx
+++ b/공정모델링/레시피_계산기.xlsx
@@ -547,7 +547,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>측정직경이 실제 PD와 같아지는 '정점'. ⚠ 봉우리가 날카로워 kV+1이면 벌써 ~20% 작게 측정됨 → 트림은 ±0.5kV 이내, 정밀 세팅 필수</t>
+          <t>측정직경이 실제 PD와 같아지는 '정점'(≈60, B3 실측 정점 59.9). ⚠ 창이 매우 좁음: B3에서 ±0.5kV(59.5·60.5)는 둘 다 게이트 탈락 → 실질 트림 ±0.3kV. 비대칭(높은 쪽 낙폭 2.6배) → 오차 시 살짝 낮게(kV↓) 치우치는 게 안전</t>
         </is>
       </c>
     </row>

--- a/공정모델링/레시피_계산기.xlsx
+++ b/공정모델링/레시피_계산기.xlsx
@@ -782,7 +782,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>⚠ 가장 중요: 봉우리가 날카로움. PhaseB 실측상 kV+1이면 벌써 ~20% 작게 측정됨. 그래서 트림 ±0.5kV, 정점 정밀 세팅이 핵심. kV 드리프트가 최대 리스크.</t>
+          <t>⚠ 가장 중요: 봉우리가 날카롭고 비대칭. B3 실측상 정점 60에서 ±0.5kV(59.5·60.5)면 이미 게이트 탈락, 특히 +0.5kV는 7.8%p 급락(−0.5kV의 2.6배). → 실질 트림 ±0.3kV, 오차 시 살짝 낮게(kV↓) 치우치는 게 안전. 정점 정밀 세팅·kV 드리프트 관리가 직경 정확도의 최대 리스크.</t>
         </is>
       </c>
     </row>

--- a/공정모델링/레시피_계산기.xlsx
+++ b/공정모델링/레시피_계산기.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -575,127 +575,148 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
+          <t>└ 예측 진원도 Roundness</t>
+        </is>
+      </c>
+      <c r="B11" s="5">
+        <f>ROUND((96.6493+0.01733*B5)/100,3)</f>
+        <v/>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0~1</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>위 kV에서 얻는 진원도(1=완전 원형). kV도 진원도의 정점(26µm~59.4·86µm~60.5)이라 직경과 같은 kV60에서 함께 최적. 26µm~0.97·86µm~0.98. 큰 범프일수록 원형</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>R (해상도용 픽셀크기)</t>
         </is>
       </c>
-      <c r="B11" s="5">
+      <c r="B12" s="5">
         <f>ROUND(B5*0.2828/14,2)</f>
         <v/>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>µm/px</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>8% void를 겨우 볼 수 있는 '가장 큰(=가장 안전한) 픽셀'. 큰 R일수록 픽셀당 광자↑ → 측정 안정. 공식 R=D·√0.08/14</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>└ 사용 가능 범위</t>
-        </is>
-      </c>
-      <c r="B12" s="5">
-        <f>"0.2 ~ "&amp;TEXT(B11,"0.00")</f>
-        <v/>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>µm/px</t>
-        </is>
-      </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>이보다 크면 void를 못 봄(해상도 부족). 이보다 작으면(→0.2) 픽셀이 광자를 굶어 측정 실패(26µm R0.2~0.25 실측 실패). 8%보다 작은 void를 잡을 때만 R을 낮추고, 그땐 F·W로 광자 보충 필요</t>
+          <t>8% void를 겨우 볼 수 있는 '가장 큰(=가장 안전한) 픽셀'. 큰 R일수록 픽셀당 광자↑ → 측정 안정. 공식 R=D·√0.08/14. (진원도엔 R 영향 미미 ~1%p → 직경·void 기준으로 결정해도 무방)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>F (프레임 수)</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>32</v>
+          <t>└ 사용 가능 범위</t>
+        </is>
+      </c>
+      <c r="B13" s="5">
+        <f>"0.2 ~ "&amp;TEXT(B12,"0.00")</f>
+        <v/>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>장(최소)</t>
+          <t>µm/px</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>여러 장 평균 → 랜덤 노이즈 저감용. 그런데 지금 노이즈가 이미 극히 작아(σ≈0.15%) 더 평균낼 필요가 없어서 최소값. 직경엔 영향 없음(실측 편차 0.28%p)</t>
+          <t>이보다 크면 void를 못 봄(해상도 부족). 이보다 작으면(→0.2) 픽셀이 광자를 굶어 측정 실패(26µm R0.2~0.25 실측 실패). 8%보다 작은 void를 잡을 때만 R을 낮추고, 그땐 F·W로 광자 보충 필요</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
+          <t>F (프레임 수)</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>장(최소)</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>여러 장 평균 → 랜덤 노이즈 저감용. 지금 노이즈가 이미 극히 작아(σ≈0.15%) 최소값. 직경엔 영향 없음(편차 0.28%p), 진원도에도 영향 미미</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>W (선속=밝기)</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B15" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>(최소)</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>범프 내부가 어두울 때 밝혀주는 값. 현재 자재(26·86µm)는 얇아서 내부가 안 어두워 효과 없음(실측 W4=W6) → 최소값. 두꺼운 자재 오면 재검토</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>범프 내부가 어두울 때 밝혀주는 값. 현재 자재(26·86µm)는 얇아서 효과 없음(직경·진원도 둘 다 무영향) → 최소값. 두꺼운 자재 오면 재검토</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>예상 Tact (검사시간)</t>
         </is>
       </c>
-      <c r="B15" s="5">
-        <f>ROUND(119.098+(0.03907+-0.01071*B13/64)*B6,0)</f>
+      <c r="B16" s="5">
+        <f>ROUND(119.098+(0.03907+-0.01071*B14/64)*B6,0)</f>
         <v/>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>초</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>대략치. 범프 수·F로 추정(예비 모델이라 오차 큼)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>■ 한 줄 요약</t>
-        </is>
-      </c>
-    </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>kV=직경 정확도(정점에 정밀 고정) · R=void 해상도+광자 안전(상한이 최적) · F=노이즈용인데 이미 충분해 최소 · W=밝기용인데 자재가 얇아 불필요해 최소. → 지금 자재·스펙에선 kV만 신경 쓰면 되고 R은 공식으로, F·W는 최소로 확정. 자세한 이유는 '추천값_설명' 시트.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>■ 직경+진원도 통합 결론</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>직경과 진원도는 둘 다 kV 정점(≈60)에서 최고 → 충돌 없이 kV60 하나로 동시 최적화됨. R·F·W는 직경에도 진원도에도 영향이 미미(≤~1%p)해, R은 void 해상도(N8 상한)로·F·W는 최소로 정하면 됨. → 통합 최적 레시피 = kV60(정밀) · R=공식 · F32 · W4. 진원도는 자재가 클수록 좋아지고, kV가 정점을 벗어나면(특히 26µm·고kV) 나빠짐. 자세한 근거는 '추천값_설명' 시트.</t>
+        </is>
+      </c>
+    </row>
     <row r="20"/>
     <row r="21"/>
+    <row r="22"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A18:E21"/>
+    <mergeCell ref="A19:E22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -707,14 +728,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -870,23 +891,51 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="78" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>요약</t>
+          <t>[결과 지표] 진원도
+(Roundness)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>kV=정확도 / R=해상도+광자안전 / F=재현성(이미 충분) / W=밝기(자재 얇아 불필요). 직경 정확도는 kV 하나가 지배하고, R은 공식으로, F·W는 '필요 없어서 최소'로 정해집니다.</t>
+          <t>측정된 범프가 얼마나 원(circle)에 가까운가(%, 100=완전 원형). 파라미터가 아니라 레시피의 '품질 결과'.</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>품질 지표 — 범프 형상 정상 여부. 직경과 함께 검사 신뢰도를 봄.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>별도로 정할 게 아니라 kV·R·F·W가 정해지면 따라 나옴. kV 정점(26µm~59·86µm~61)에서 최고 → 직경과 같은 kV60에서 동시 최적.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>실측: 정점에서 26µm~97%·86µm~98%. 큰 범프일수록 원형. kV가 정점 벗어나면(특히 26µm·고kV62) 하락(최저 91%). R·F·W 효과는 ~1%p로 미미.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>통합 결론</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>kV=정확도+진원도(둘 다 정점 60) / R=해상도+광자안전(진원도 영향 미미) / F=재현성(이미 충분) / W=밝기(자재 얇아 불필요). → 직경과 진원도가 같은 kV60을 요구해 충돌이 없고, 통합 최적 레시피는 kV60·R(공식)·F32·W4로 하나로 정해집니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B12:E12"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B10:E10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -995,7 +1044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1161,13 +1210,151 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>진원도 모델 계수 (roundness% = b0 + b_kV·kV + b_kV2·kV² + b_R·R + b_F·F + b_W·W)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>anchor</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>b0</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>b_kV</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>b_kV2</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>b_R</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>b_F</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>b_W</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>정점kV</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Rnd%@정점</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>R²</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>D26</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>26</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-1516.623</v>
+      </c>
+      <c r="D10" t="n">
+        <v>54.4035</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.45802</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-4.7202</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001042</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.12329</v>
+      </c>
+      <c r="I10" t="n">
+        <v>59.39</v>
+      </c>
+      <c r="J10" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.7569</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>D86</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>86</v>
+      </c>
+      <c r="C11" t="n">
+        <v>426.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-10.8615</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.0897</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4674</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.000724</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.04118</v>
+      </c>
+      <c r="I11" t="n">
+        <v>60.55</v>
+      </c>
+      <c r="J11" t="n">
+        <v>98.14</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.6885</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Tact 모델</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>tact = 119.098 + 0.03907·bump + -0.01071·bump·(F/64), R²=0.3304</t>
         </is>

--- a/공정모델링/레시피_계산기.xlsx
+++ b/공정모델링/레시피_계산기.xlsx
@@ -589,7 +589,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>위 kV에서 얻는 진원도(1=완전 원형). kV도 진원도의 정점(26µm~59.4·86µm~60.5)이라 직경과 같은 kV60에서 함께 최적. 26µm~0.97·86µm~0.98. 큰 범프일수록 원형</t>
+          <t>위 kV에서 얻는 진원도(1=완전 원형). kV가 정점(26µm~59.4·86µm~60.5)일 때 최고 → 직경과 같은 kV60에서 함께 최적. 26µm~0.97·86µm~0.98. 큰 범프일수록 원형. ※ R도 소폭 영향(거친 R일수록 원형↑, Δ~1%p) — 아래 추천 R(거친 쪽)에서 진원도도 최고. F·W는 무의미(Δ&lt;0.4%p)</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8% void를 겨우 볼 수 있는 '가장 큰(=가장 안전한) 픽셀'. 큰 R일수록 픽셀당 광자↑ → 측정 안정. 공식 R=D·√0.08/14. (진원도엔 R 영향 미미 ~1%p → 직경·void 기준으로 결정해도 무방)</t>
+          <t>8% void를 겨우 볼 수 있는 '가장 큰(=가장 안전한) 픽셀'. 큰 R일수록 픽셀당 광자↑ → 측정 안정, 게다가 진원도도 소폭↑(거친 R=매끈). 공식 R=D·√0.08/14. 반대로 R을 낮추면(작은 void 검출) 진원도가 ~1%p 손해(특히 26µm R0.35=96%)</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>직경과 진원도는 둘 다 kV 정점(≈60)에서 최고 → 충돌 없이 kV60 하나로 동시 최적화됨. R·F·W는 직경에도 진원도에도 영향이 미미(≤~1%p)해, R은 void 해상도(N8 상한)로·F·W는 최소로 정하면 됨. → 통합 최적 레시피 = kV60(정밀) · R=공식 · F32 · W4. 진원도는 자재가 클수록 좋아지고, kV가 정점을 벗어나면(특히 26µm·고kV) 나빠짐. 자세한 근거는 '추천값_설명' 시트.</t>
+          <t>직경과 진원도는 둘 다 kV 정점(≈60)에서 최고 → 충돌 없이 kV60 하나로 동시 최적화됨. R은 직경엔 무영향이지만 진원도엔 소폭(거친 R=원형↑, Δ~1%p) — 추천 R(void 게이트의 거친 쪽)에서 진원도도 최고라 방향이 일치. F·W는 직경·진원도 둘 다 무의미. → 통합 최적 레시피 = kV60(정밀) · R=공식(거친 쪽) · F32 · W4. 단 void 위해 R을 낮추면 진원도 ~1%p 손해. 진원도는 자재가 클수록 좋아짐. 자세한 근거는 '추천값_설명' 시트.</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>실측: 정점에서 26µm~97%·86µm~98%. 큰 범프일수록 원형. kV가 정점 벗어나면(특히 26µm·고kV62) 하락(최저 91%). R·F·W 효과는 ~1%p로 미미.</t>
+          <t>실측(kV 정점 고정 후): 정점 진원도 26µm~97%·86µm~98%. 큰 범프일수록 원형. kV 정점 이탈 시(특히 26µm 고kV62) 최저 91%. R은 소폭 실효(거친 R일수록 원형↑, Δ~1%p; 26µm R0.35=96%가 최저) — 추천 R(거친 쪽)에서 진원도도 최고라 방향 일치. F(Δ&lt;0.4%p)·W(Δ&lt;0.2%p)는 무의미.</t>
         </is>
       </c>
     </row>
